--- a/outputs/Block5_Most_Stable.xlsx
+++ b/outputs/Block5_Most_Stable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="51">
   <si>
     <t>Variable</t>
   </si>
@@ -109,48 +109,48 @@
     <t>RSenLeanResH  (&gt;1&lt;=5%)</t>
   </si>
   <si>
+    <t>RHouLikResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>RHouLeanResH  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>RHouSafResH (&gt;10%)</t>
+  </si>
+  <si>
+    <t>DHouTiltResLR (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>DSenLeanResH  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>DHouTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>RHouSafResLD (&gt;10%)</t>
+  </si>
+  <si>
+    <t>RHouTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>DHouLikResLR (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
     <t>DSenLeanResLR  (&gt;1&lt;=5%)</t>
   </si>
   <si>
+    <t>DHouSafResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>DHouSafResLR (&gt;10%)</t>
+  </si>
+  <si>
     <t>DHouLeanResH  (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>DSenLeanResH  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>DHouSafResLR (&gt;10%)</t>
-  </si>
-  <si>
-    <t>RSenSafResLD (&gt;10%)</t>
-  </si>
-  <si>
-    <t>DHouLikResLR (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>DSenTiltResLR (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>DHouLeanResLR  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>DSenLikResLR (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RHouSafResLD (&gt;10%)</t>
-  </si>
-  <si>
     <t>RSenTiltResLD (&lt;=1%)</t>
   </si>
   <si>
-    <t>DSenLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RHouLikResLD (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RHouLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
     <t>Senate Buckets</t>
   </si>
   <si>
@@ -167,9 +167,6 @@
   </si>
   <si>
     <t>Moderate-low sensitivity</t>
-  </si>
-  <si>
-    <t>Moderate sensitivity</t>
   </si>
 </sst>
 </file>
@@ -663,10 +660,10 @@
         <v>47</v>
       </c>
       <c r="P2">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="Q2">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -675,10 +672,10 @@
         <v>48</v>
       </c>
       <c r="T2">
-        <v>0.1597411054555158</v>
+        <v>0.141286249557361</v>
       </c>
       <c r="U2">
-        <v>-0.1597411054555158</v>
+        <v>-0.141286249557361</v>
       </c>
       <c r="V2" t="s">
         <v>6</v>
@@ -704,82 +701,82 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3">
-        <v>0.66</v>
+        <v>15.048</v>
       </c>
       <c r="D3">
-        <v>0.756</v>
+        <v>14.824</v>
       </c>
       <c r="E3">
-        <v>0.8217382316493707</v>
+        <v>15.00521451603779</v>
       </c>
       <c r="F3">
-        <v>0.6</v>
+        <v>14.2</v>
       </c>
       <c r="G3">
-        <v>0.7051224071145452</v>
+        <v>14.93988810988627</v>
       </c>
       <c r="J3" t="s">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>0.8217382316493707</v>
+        <v>15.00521451603779</v>
       </c>
       <c r="L3">
-        <v>1.559831022862906</v>
+        <v>6.129350049043507</v>
       </c>
       <c r="M3">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N3">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="O3" t="s">
         <v>47</v>
       </c>
       <c r="P3">
-        <v>0.6715511146470821</v>
+        <v>14.85295632081913</v>
       </c>
       <c r="Q3">
-        <v>0.8172324090351291</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S3" t="s">
         <v>48</v>
       </c>
       <c r="T3">
-        <v>-0.1501871170022886</v>
+        <v>-0.152258195218657</v>
       </c>
       <c r="U3">
-        <v>0.3284488853529179</v>
+        <v>0.1470436791808698</v>
       </c>
       <c r="V3" t="s">
         <v>6</v>
       </c>
       <c r="W3">
-        <v>0.7051224071145452</v>
+        <v>14.93988810988627</v>
       </c>
       <c r="X3">
-        <v>0.1166158245348254</v>
+        <v>0.06532640615151664</v>
       </c>
       <c r="Y3">
-        <v>0.1782617683506293</v>
+        <v>0.00521451603778722</v>
       </c>
       <c r="Z3">
-        <v>0.0747618317789252</v>
+        <v>0.01065796628171219</v>
       </c>
       <c r="AA3">
-        <v>0.1142827432829542</v>
+        <v>0.0008507453475594778</v>
       </c>
       <c r="AB3">
-        <v>1.299859185719089</v>
+        <v>0.972912706197382</v>
       </c>
       <c r="AC3">
-        <v>91.52169382676631</v>
+        <v>99.2800601772977</v>
       </c>
       <c r="AD3" t="s">
         <v>49</v>
@@ -793,79 +790,79 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>7.9</v>
+        <v>13.316</v>
       </c>
       <c r="D4">
-        <v>8.827999999999999</v>
+        <v>12.472</v>
       </c>
       <c r="E4">
-        <v>7.820194910667125</v>
+        <v>12.98388364583827</v>
       </c>
       <c r="F4">
-        <v>9.4</v>
+        <v>11.8</v>
       </c>
       <c r="G4">
-        <v>8.347892116185454</v>
+        <v>12.9086498426072</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>7.820194910667125</v>
+        <v>12.98388364583827</v>
       </c>
       <c r="L4">
-        <v>4.467028425282805</v>
+        <v>3.125306797245826</v>
       </c>
       <c r="M4">
         <v>5.24749619700716</v>
       </c>
       <c r="N4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="s">
         <v>47</v>
       </c>
       <c r="P4">
-        <v>8.056225323873495</v>
+        <v>12.85213593315269</v>
       </c>
       <c r="Q4">
-        <v>1.030182165010288</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R4">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="S4" t="s">
         <v>48</v>
       </c>
       <c r="T4">
-        <v>0.23603041320637</v>
+        <v>-0.1317477126855753</v>
       </c>
       <c r="U4">
-        <v>-0.05622532387349466</v>
+        <v>0.1478640668473066</v>
       </c>
       <c r="V4" t="s">
         <v>6</v>
       </c>
       <c r="W4">
-        <v>8.347892116185454</v>
+        <v>12.9086498426072</v>
       </c>
       <c r="X4">
-        <v>0.5276972055183293</v>
+        <v>0.07523380323107176</v>
       </c>
       <c r="Y4">
-        <v>0.1798050893328753</v>
+        <v>0.01611635416173129</v>
       </c>
       <c r="Z4">
-        <v>0.1181315978496199</v>
+        <v>0.02407245371794266</v>
       </c>
       <c r="AA4">
-        <v>0.04025161073862921</v>
+        <v>0.005156727069462051</v>
       </c>
       <c r="AB4">
-        <v>0.911638454139348</v>
+        <v>0.6511055827595471</v>
       </c>
       <c r="AC4">
-        <v>91.31331214761543</v>
+        <v>98.2699453837879</v>
       </c>
       <c r="AD4" t="s">
         <v>49</v>
@@ -876,85 +873,85 @@
         <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5">
-        <v>1.124</v>
+        <v>172.1</v>
       </c>
       <c r="D5">
-        <v>1.364</v>
+        <v>175.156</v>
       </c>
       <c r="E5">
-        <v>1.289478939532622</v>
+        <v>175.5898630732044</v>
       </c>
       <c r="F5">
-        <v>1.4</v>
+        <v>172.6</v>
       </c>
       <c r="G5">
-        <v>1.236806017786363</v>
+        <v>173.5749550722659</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>1.289478939532622</v>
+        <v>175.5898630732044</v>
       </c>
       <c r="L5">
-        <v>0.9319718387197466</v>
+        <v>24.70132137894479</v>
       </c>
       <c r="M5">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N5">
-        <v>0.9</v>
+        <v>18.7</v>
       </c>
       <c r="O5" t="s">
         <v>47</v>
       </c>
       <c r="P5">
-        <v>1.053803980154308</v>
+        <v>173.8081494148196</v>
       </c>
       <c r="Q5">
-        <v>0.8172324090351291</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <v>174</v>
       </c>
       <c r="S5" t="s">
         <v>48</v>
       </c>
       <c r="T5">
-        <v>-0.2356749593783138</v>
+        <v>-1.781713658384717</v>
       </c>
       <c r="U5">
-        <v>-0.05380398015430821</v>
+        <v>0.1918505851803616</v>
       </c>
       <c r="V5" t="s">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>1.236806017786363</v>
+        <v>173.5749550722659</v>
       </c>
       <c r="X5">
-        <v>0.05267292174625871</v>
+        <v>2.014908000938448</v>
       </c>
       <c r="Y5">
-        <v>0.289478939532622</v>
+        <v>1.589863073204356</v>
       </c>
       <c r="Z5">
-        <v>0.05651771819480694</v>
+        <v>0.08157085890376452</v>
       </c>
       <c r="AA5">
-        <v>0.3106091058827276</v>
+        <v>0.06436348277948976</v>
       </c>
       <c r="AB5">
-        <v>1.035524265244163</v>
+        <v>1.320926276948919</v>
       </c>
       <c r="AC5">
-        <v>86.46333766795863</v>
+        <v>92.72349650896915</v>
       </c>
       <c r="AD5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -965,82 +962,82 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>3.096</v>
+        <v>1.412</v>
       </c>
       <c r="D6">
-        <v>4.516</v>
+        <v>1.808</v>
       </c>
       <c r="E6">
-        <v>-5.436536811828134</v>
+        <v>1.699906626866217</v>
       </c>
       <c r="F6">
-        <v>7.4</v>
+        <v>2.2</v>
       </c>
       <c r="G6">
-        <v>3.781352160542397</v>
+        <v>1.603126377165344</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1.699906626866217</v>
       </c>
       <c r="L6">
-        <v>9.933150479214353</v>
+        <v>1.746417103282563</v>
       </c>
       <c r="M6">
         <v>5.24749619700716</v>
       </c>
       <c r="N6">
-        <v>10.3</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="s">
         <v>47</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.717926703142854</v>
       </c>
       <c r="Q6">
-        <v>1.030182165010288</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" t="s">
         <v>48</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.01802007627663649</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>0.2820732968571464</v>
       </c>
       <c r="V6" t="s">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>3.781352160542397</v>
+        <v>1.603126377165344</v>
       </c>
       <c r="X6">
-        <v>3.781352160542397</v>
+        <v>0.09678024970087273</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>0.3000933731337829</v>
       </c>
       <c r="Z6">
-        <v>0.3806800439050106</v>
+        <v>0.05541645779748992</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.1718337346615124</v>
       </c>
       <c r="AB6">
-        <v>0.9643835416712964</v>
+        <v>0.7593117840358968</v>
       </c>
       <c r="AC6">
-        <v>78.07954833544376</v>
+        <v>90.83163983910151</v>
       </c>
       <c r="AD6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -1051,82 +1048,82 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>0.656</v>
+        <v>1.164</v>
       </c>
       <c r="D7">
-        <v>0.384</v>
+        <v>1.34</v>
       </c>
       <c r="E7">
-        <v>0.4366083165842541</v>
+        <v>1.234402433809649</v>
       </c>
       <c r="F7">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="G7">
-        <v>0.5281531798421215</v>
+        <v>1.246724413043333</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
       <c r="K7">
-        <v>0.4366083165842541</v>
+        <v>1.234402433809649</v>
       </c>
       <c r="L7">
-        <v>0.7620693762924241</v>
+        <v>0.9319718387197466</v>
       </c>
       <c r="M7">
         <v>1.038416113387647</v>
       </c>
       <c r="N7">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O7" t="s">
         <v>47</v>
       </c>
       <c r="P7">
-        <v>0.5063526117264946</v>
+        <v>1.06279383028951</v>
       </c>
       <c r="Q7">
-        <v>1.159741105455516</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="s">
         <v>48</v>
       </c>
       <c r="T7">
-        <v>0.06974429514224045</v>
+        <v>-0.1716086035201392</v>
       </c>
       <c r="U7">
-        <v>-0.5063526117264946</v>
+        <v>-0.06279383028951013</v>
       </c>
       <c r="V7" t="s">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>0.5281531798421215</v>
+        <v>1.246724413043333</v>
       </c>
       <c r="X7">
-        <v>0.09154486325786737</v>
+        <v>0.01232197923368372</v>
       </c>
       <c r="Y7">
-        <v>0.4366083165842541</v>
+        <v>0.2344024338096493</v>
       </c>
       <c r="Z7">
-        <v>0.1201266788901112</v>
+        <v>0.0132214072590546</v>
       </c>
       <c r="AA7">
-        <v>0.5729246314927595</v>
+        <v>0.2515123569953024</v>
       </c>
       <c r="AB7">
-        <v>0.95258672036553</v>
+        <v>1.035524265244163</v>
       </c>
       <c r="AC7">
-        <v>75.68380671977501</v>
+        <v>90.78980016577228</v>
       </c>
       <c r="AD7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -1137,82 +1134,82 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>2.568</v>
+        <v>1.128</v>
       </c>
       <c r="D8">
-        <v>3.732</v>
+        <v>1.252</v>
       </c>
       <c r="E8">
-        <v>-3.223234081728676</v>
+        <v>1.026071324842432</v>
       </c>
       <c r="F8">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="G8">
-        <v>3.129795714698134</v>
+        <v>1.187847653455815</v>
       </c>
       <c r="J8" t="s">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1.026071324842432</v>
       </c>
       <c r="L8">
-        <v>7.059923274159115</v>
+        <v>0.8200692764238203</v>
       </c>
       <c r="M8">
         <v>5.24749619700716</v>
       </c>
       <c r="N8">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="s">
         <v>47</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.036948324347409</v>
       </c>
       <c r="Q8">
-        <v>1.030182165010288</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="s">
         <v>48</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.01087699950497645</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>-0.03694832434740891</v>
       </c>
       <c r="V8" t="s">
         <v>6</v>
       </c>
       <c r="W8">
-        <v>3.129795714698134</v>
+        <v>1.187847653455815</v>
       </c>
       <c r="X8">
-        <v>3.129795714698134</v>
+        <v>0.1617763286133824</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>0.02607132484243246</v>
       </c>
       <c r="Z8">
-        <v>0.4433186584553801</v>
+        <v>0.1972715394470829</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>0.03179161272340916</v>
       </c>
       <c r="AB8">
-        <v>0.9289372729156731</v>
+        <v>0.7455175240216548</v>
       </c>
       <c r="AC8">
-        <v>74.96437929576021</v>
+        <v>86.99204005901876</v>
       </c>
       <c r="AD8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:30">
@@ -1220,85 +1217,85 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9">
-        <v>0.216</v>
+        <v>5.304</v>
       </c>
       <c r="D9">
-        <v>0.18</v>
+        <v>4.316</v>
       </c>
       <c r="E9">
-        <v>0.01190808928740122</v>
+        <v>4.035405960595082</v>
       </c>
       <c r="F9">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="G9">
-        <v>0.1990790973320455</v>
+        <v>4.827149341819798</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>0.01190808928740122</v>
+        <v>4.035405960595082</v>
       </c>
       <c r="L9">
-        <v>0.421748166646455</v>
+        <v>2.858585552684069</v>
       </c>
       <c r="M9">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N9">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="s">
         <v>47</v>
       </c>
       <c r="P9">
-        <v>0.009731676495348316</v>
+        <v>3.994458620063688</v>
       </c>
       <c r="Q9">
-        <v>0.8172324090351291</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S9" t="s">
         <v>48</v>
       </c>
       <c r="T9">
-        <v>-0.002176412792052908</v>
+        <v>-0.04094734053139382</v>
       </c>
       <c r="U9">
-        <v>-0.009731676495348316</v>
+        <v>0.005541379936312207</v>
       </c>
       <c r="V9" t="s">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>0.1990790973320455</v>
+        <v>4.827149341819798</v>
       </c>
       <c r="X9">
-        <v>0.1871710080446443</v>
+        <v>0.7917433812247161</v>
       </c>
       <c r="Y9">
-        <v>0.01190808928740122</v>
+        <v>0.03540596059508161</v>
       </c>
       <c r="Z9">
-        <v>0.4437980360008223</v>
+        <v>0.2769703290780675</v>
       </c>
       <c r="AA9">
-        <v>0.02823507066335061</v>
+        <v>0.01238583206363622</v>
       </c>
       <c r="AB9">
-        <v>1.054370416616137</v>
+        <v>0.6972159884595291</v>
       </c>
       <c r="AC9">
-        <v>74.20408390839145</v>
+        <v>83.16315746844765</v>
       </c>
       <c r="AD9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:30">
@@ -1309,82 +1306,82 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>3.516</v>
+        <v>3.692</v>
       </c>
       <c r="D10">
-        <v>4.924</v>
+        <v>3.192</v>
       </c>
       <c r="E10">
-        <v>5.173756282914196</v>
+        <v>3.475459163737268</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>4.195560452143448</v>
+        <v>3.450678816710424</v>
       </c>
       <c r="J10" t="s">
         <v>4</v>
       </c>
       <c r="K10">
-        <v>5.173756282914196</v>
+        <v>3.475459163737268</v>
       </c>
       <c r="L10">
-        <v>2.262338789582505</v>
+        <v>0.887818750560327</v>
       </c>
       <c r="M10">
         <v>5.24749619700716</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="s">
         <v>47</v>
       </c>
       <c r="P10">
-        <v>5.329911448768128</v>
+        <v>3.440193613933819</v>
       </c>
       <c r="Q10">
-        <v>1.030182165010288</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S10" t="s">
         <v>48</v>
       </c>
       <c r="T10">
-        <v>0.1561551658539315</v>
+        <v>-0.03526554980344976</v>
       </c>
       <c r="U10">
-        <v>-0.3299114487681276</v>
+        <v>-0.4401936139338187</v>
       </c>
       <c r="V10" t="s">
         <v>6</v>
       </c>
       <c r="W10">
-        <v>4.195560452143448</v>
+        <v>3.450678816710424</v>
       </c>
       <c r="X10">
-        <v>0.9781958307707486</v>
+        <v>0.0247803470268444</v>
       </c>
       <c r="Y10">
-        <v>0.1737562829141961</v>
+        <v>0.4754591637372685</v>
       </c>
       <c r="Z10">
-        <v>0.4323825570578075</v>
+        <v>0.02791149320872625</v>
       </c>
       <c r="AA10">
-        <v>0.07680382960956141</v>
+        <v>0.5355362943587225</v>
       </c>
       <c r="AB10">
-        <v>0.452467757916501</v>
+        <v>0.3551275002241308</v>
       </c>
       <c r="AC10">
-        <v>73.49667620805681</v>
+        <v>81.41748166151876</v>
       </c>
       <c r="AD10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -1392,85 +1389,85 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11">
-        <v>0.652</v>
+        <v>3.184</v>
       </c>
       <c r="D11">
-        <v>0.612</v>
+        <v>4.004</v>
       </c>
       <c r="E11">
-        <v>0.2977289224579263</v>
+        <v>1.550377686812013</v>
       </c>
       <c r="F11">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="G11">
-        <v>0.633198997035606</v>
+        <v>3.579766740594905</v>
       </c>
       <c r="J11" t="s">
         <v>4</v>
       </c>
       <c r="K11">
-        <v>0.2977289224579263</v>
+        <v>1.550377686812013</v>
       </c>
       <c r="L11">
-        <v>1.005444112310955</v>
+        <v>7.059923274159115</v>
       </c>
       <c r="M11">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N11">
-        <v>0.9</v>
+        <v>7.6</v>
       </c>
       <c r="O11" t="s">
         <v>47</v>
       </c>
       <c r="P11">
-        <v>0.2433137245397242</v>
+        <v>1.566812662552681</v>
       </c>
       <c r="Q11">
-        <v>0.8172324090351291</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="s">
         <v>48</v>
       </c>
       <c r="T11">
-        <v>-0.05441519791820207</v>
+        <v>0.01643497574066832</v>
       </c>
       <c r="U11">
-        <v>-0.2433137245397242</v>
+        <v>0.433187337447319</v>
       </c>
       <c r="V11" t="s">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>0.633198997035606</v>
+        <v>3.579766740594905</v>
       </c>
       <c r="X11">
-        <v>0.3354700745776797</v>
+        <v>2.029389053782892</v>
       </c>
       <c r="Y11">
-        <v>0.2977289224579263</v>
+        <v>0.4496223131879873</v>
       </c>
       <c r="Z11">
-        <v>0.3336536267606375</v>
+        <v>0.2874519984106493</v>
       </c>
       <c r="AA11">
-        <v>0.296116829182692</v>
+        <v>0.06368657218042365</v>
       </c>
       <c r="AB11">
-        <v>1.117160124789949</v>
+        <v>0.9289372729156731</v>
       </c>
       <c r="AC11">
-        <v>72.57746240041317</v>
+        <v>81.12864354622022</v>
       </c>
       <c r="AD11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:30">
@@ -1478,85 +1475,85 @@
         <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12">
-        <v>5.232</v>
+        <v>0.612</v>
       </c>
       <c r="D12">
-        <v>4.208</v>
+        <v>0.732</v>
       </c>
       <c r="E12">
-        <v>3.696547591818899</v>
+        <v>0.3293773794100608</v>
       </c>
       <c r="F12">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="G12">
-        <v>4.737774216622949</v>
+        <v>0.6684030088931816</v>
       </c>
       <c r="J12" t="s">
         <v>4</v>
       </c>
       <c r="K12">
-        <v>3.696547591818899</v>
+        <v>0.3293773794100608</v>
       </c>
       <c r="L12">
-        <v>2.858585552684069</v>
+        <v>1.559831022862906</v>
       </c>
       <c r="M12">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N12">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="O12" t="s">
         <v>47</v>
       </c>
       <c r="P12">
-        <v>3.461204303080457</v>
+        <v>0.2835868085528425</v>
       </c>
       <c r="Q12">
-        <v>0.9363343003457338</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="s">
         <v>48</v>
       </c>
       <c r="T12">
-        <v>-0.2353432887384428</v>
+        <v>-0.04579057085721838</v>
       </c>
       <c r="U12">
-        <v>-0.4612043030804567</v>
+        <v>-0.2835868085528425</v>
       </c>
       <c r="V12" t="s">
         <v>6</v>
       </c>
       <c r="W12">
-        <v>4.737774216622949</v>
+        <v>0.6684030088931816</v>
       </c>
       <c r="X12">
-        <v>1.041226624804049</v>
+        <v>0.3390256294831208</v>
       </c>
       <c r="Y12">
-        <v>0.6965475918188995</v>
+        <v>0.3293773794100608</v>
       </c>
       <c r="Z12">
-        <v>0.3642453953586904</v>
+        <v>0.2173476642751179</v>
       </c>
       <c r="AA12">
-        <v>0.2436686182664276</v>
+        <v>0.2111622185879616</v>
       </c>
       <c r="AB12">
-        <v>0.6972159884595291</v>
+        <v>1.299859185719089</v>
       </c>
       <c r="AC12">
-        <v>72.46666497041721</v>
+        <v>80.63940515159102</v>
       </c>
       <c r="AD12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:30">
@@ -1564,85 +1561,85 @@
         <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13">
-        <v>0.656</v>
+        <v>172.984</v>
       </c>
       <c r="D13">
-        <v>0.384</v>
+        <v>170.488</v>
       </c>
       <c r="E13">
-        <v>0.4366083165842541</v>
+        <v>172.6467820636017</v>
       </c>
       <c r="F13">
-        <v>0.4</v>
+        <v>169.2</v>
       </c>
       <c r="G13">
-        <v>0.5281531798421215</v>
+        <v>171.7793246530184</v>
       </c>
       <c r="J13" t="s">
         <v>4</v>
       </c>
       <c r="K13">
-        <v>0.4366083165842541</v>
+        <v>172.6467820636017</v>
       </c>
       <c r="L13">
-        <v>0.7620693762924241</v>
+        <v>4.764861070548267</v>
       </c>
       <c r="M13">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N13">
-        <v>0.8</v>
+        <v>13.2</v>
       </c>
       <c r="O13" t="s">
         <v>47</v>
       </c>
       <c r="P13">
-        <v>0.5063526117264946</v>
+        <v>174.4769462223457</v>
       </c>
       <c r="Q13">
-        <v>1.159741105455516</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>174</v>
       </c>
       <c r="S13" t="s">
         <v>48</v>
       </c>
       <c r="T13">
-        <v>0.06974429514224045</v>
+        <v>1.830164158743969</v>
       </c>
       <c r="U13">
-        <v>0.4936473882735054</v>
+        <v>-0.4769462223457026</v>
       </c>
       <c r="V13" t="s">
         <v>6</v>
       </c>
       <c r="W13">
-        <v>0.5281531798421215</v>
+        <v>171.7793246530184</v>
       </c>
       <c r="X13">
-        <v>0.09154486325786737</v>
+        <v>0.8674574105832846</v>
       </c>
       <c r="Y13">
-        <v>0.5633916834157459</v>
+        <v>1.353217936398266</v>
       </c>
       <c r="Z13">
-        <v>0.1201266788901112</v>
+        <v>0.1820530331818197</v>
       </c>
       <c r="AA13">
-        <v>0.7392918557582336</v>
+        <v>0.2839994527358924</v>
       </c>
       <c r="AB13">
-        <v>0.95258672036553</v>
+        <v>0.3609743235263839</v>
       </c>
       <c r="AC13">
-        <v>71.40270081666996</v>
+        <v>80.43391422492162</v>
       </c>
       <c r="AD13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:30">
@@ -1650,46 +1647,46 @@
         <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14">
-        <v>1.868</v>
+        <v>3.948</v>
       </c>
       <c r="D14">
-        <v>1.492</v>
+        <v>4.92</v>
       </c>
       <c r="E14">
-        <v>1.186511751275934</v>
+        <v>1.16567981478854</v>
       </c>
       <c r="F14">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="G14">
-        <v>1.691270572134697</v>
+        <v>4.417128380314937</v>
       </c>
       <c r="J14" t="s">
         <v>4</v>
       </c>
       <c r="K14">
-        <v>1.186511751275934</v>
+        <v>1.16567981478854</v>
       </c>
       <c r="L14">
-        <v>1.157976831184469</v>
+        <v>9.933150479214353</v>
       </c>
       <c r="M14">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N14">
-        <v>1.4</v>
+        <v>10.3</v>
       </c>
       <c r="O14" t="s">
         <v>47</v>
       </c>
       <c r="P14">
-        <v>0.969655856843721</v>
+        <v>1.178036751837105</v>
       </c>
       <c r="Q14">
-        <v>0.8172324090351291</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -1698,37 +1695,37 @@
         <v>48</v>
       </c>
       <c r="T14">
-        <v>-0.2168558944322125</v>
+        <v>0.01235693704856522</v>
       </c>
       <c r="U14">
-        <v>0.03034414315627898</v>
+        <v>-0.1780367518371049</v>
       </c>
       <c r="V14" t="s">
         <v>6</v>
       </c>
       <c r="W14">
-        <v>1.691270572134697</v>
+        <v>4.417128380314937</v>
       </c>
       <c r="X14">
-        <v>0.5047588208587637</v>
+        <v>3.251448565526397</v>
       </c>
       <c r="Y14">
-        <v>0.1865117512759336</v>
+        <v>0.1656798147885397</v>
       </c>
       <c r="Z14">
-        <v>0.4358971675991626</v>
+        <v>0.3273330623884362</v>
       </c>
       <c r="AA14">
-        <v>0.1610669110582764</v>
+        <v>0.01667948302356171</v>
       </c>
       <c r="AB14">
-        <v>0.8271263079889064</v>
+        <v>0.9643835416712964</v>
       </c>
       <c r="AC14">
-        <v>71.19792026130897</v>
+        <v>80.36396477336831</v>
       </c>
       <c r="AD14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:30">
@@ -1739,82 +1736,82 @@
         <v>46</v>
       </c>
       <c r="C15">
-        <v>7.252</v>
+        <v>7.968</v>
       </c>
       <c r="D15">
-        <v>5.608</v>
+        <v>8.868</v>
       </c>
       <c r="E15">
-        <v>4.766317009415515</v>
+        <v>10.0582691946606</v>
       </c>
       <c r="F15">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="G15">
-        <v>6.458535949343873</v>
+        <v>8.402378129921239</v>
       </c>
       <c r="J15" t="s">
         <v>4</v>
       </c>
       <c r="K15">
-        <v>4.766317009415515</v>
+        <v>10.0582691946606</v>
       </c>
       <c r="L15">
-        <v>3.997862832988686</v>
+        <v>4.467028425282805</v>
       </c>
       <c r="M15">
         <v>5.24749619700716</v>
       </c>
       <c r="N15">
-        <v>6.7</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="s">
         <v>47</v>
       </c>
       <c r="P15">
-        <v>4.462866102237046</v>
+        <v>10.16489315578537</v>
       </c>
       <c r="Q15">
-        <v>0.9363343003457338</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R15">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="S15" t="s">
         <v>48</v>
       </c>
       <c r="T15">
-        <v>-0.3034509071784681</v>
+        <v>0.1066239611247735</v>
       </c>
       <c r="U15">
-        <v>-0.4628661022370464</v>
+        <v>-0.1648931557853732</v>
       </c>
       <c r="V15" t="s">
         <v>6</v>
       </c>
       <c r="W15">
-        <v>6.458535949343873</v>
+        <v>8.402378129921239</v>
       </c>
       <c r="X15">
-        <v>1.692218939928359</v>
+        <v>1.655891064739361</v>
       </c>
       <c r="Y15">
-        <v>0.7663170094155145</v>
+        <v>0.05826919466059977</v>
       </c>
       <c r="Z15">
-        <v>0.4232808904709982</v>
+        <v>0.3706918575595425</v>
       </c>
       <c r="AA15">
-        <v>0.1916816662873444</v>
+        <v>0.01304428562191448</v>
       </c>
       <c r="AB15">
-        <v>0.5966959452221919</v>
+        <v>0.911638454139348</v>
       </c>
       <c r="AC15">
-        <v>71.01911200459742</v>
+        <v>78.23013869485108</v>
       </c>
       <c r="AD15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:30">
@@ -1822,85 +1819,85 @@
         <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16">
-        <v>15.112</v>
+        <v>0.632</v>
       </c>
       <c r="D16">
-        <v>15.028</v>
+        <v>0.416</v>
       </c>
       <c r="E16">
-        <v>17.90152433308469</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="F16">
-        <v>14.2</v>
+        <v>0.4</v>
       </c>
       <c r="G16">
-        <v>15.07145804120735</v>
+        <v>0.530474583992273</v>
       </c>
       <c r="J16" t="s">
         <v>4</v>
       </c>
       <c r="K16">
-        <v>17.90152433308469</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="L16">
-        <v>6.129350049043507</v>
+        <v>0.7620693762924241</v>
       </c>
       <c r="M16">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N16">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="O16" t="s">
         <v>47</v>
       </c>
       <c r="P16">
-        <v>16.76181126154098</v>
+        <v>0.7484613503089816</v>
       </c>
       <c r="Q16">
-        <v>0.9363343003457338</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R16">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="S16" t="s">
         <v>48</v>
       </c>
       <c r="T16">
-        <v>-1.13971307154371</v>
+        <v>0.0926562439219849</v>
       </c>
       <c r="U16">
-        <v>0.2381887384590158</v>
+        <v>0.2515386496910184</v>
       </c>
       <c r="V16" t="s">
         <v>6</v>
       </c>
       <c r="W16">
-        <v>15.07145804120735</v>
+        <v>0.530474583992273</v>
       </c>
       <c r="X16">
-        <v>2.830066291877342</v>
+        <v>0.1253305223947238</v>
       </c>
       <c r="Y16">
-        <v>0.9015243330846943</v>
+        <v>0.3441948936130033</v>
       </c>
       <c r="Z16">
-        <v>0.4617237177241946</v>
+        <v>0.1644607778421363</v>
       </c>
       <c r="AA16">
-        <v>0.1470831859611899</v>
+        <v>0.4516582142265844</v>
       </c>
       <c r="AB16">
-        <v>0.972912706197382</v>
+        <v>0.95258672036553</v>
       </c>
       <c r="AC16">
-        <v>70.35618198382974</v>
+        <v>76.72213858724069</v>
       </c>
       <c r="AD16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
